--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/6574-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/6574-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA827506-A3F2-45E5-989C-D8F26202507B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2FD8B54B-728C-45E1-B768-8FA2843392DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{84F29A30-F912-4E9B-960C-6359AB18D008}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{F3EE2E1E-41CC-4A18-81F5-E6C424E2A796}"/>
   </bookViews>
   <sheets>
     <sheet name="6574-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1490,30 +1490,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{252CD359-3C33-46BB-94CF-2CEA79058463}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{53852342-0564-427E-991B-5355B13FE431}">
   <dimension ref="A1:X54"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="8.125" customWidth="1"/>
-    <col min="24" max="24" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="7" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1547,7 +1547,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1583,7 +1583,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1635,7 +1635,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1703,7 +1703,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1849,7 +1849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1923,7 +1923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
         <v>29</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2291,7 +2291,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2365,7 +2365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="16" t="s">
         <v>29</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
         <v>29</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="35">
         <v>2023</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>7.88</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2881,7 +2881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2955,7 +2955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
         <v>29</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2022</v>
       </c>
@@ -3249,7 +3249,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3323,7 +3323,7 @@
         <v>7.55</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
         <v>29</v>
       </c>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="16" t="s">
         <v>29</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="16" t="s">
         <v>29</v>
       </c>
@@ -3545,7 +3545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="16" t="s">
         <v>29</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="16" t="s">
         <v>29</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2021</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>29</v>
       </c>
@@ -3839,7 +3839,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>29</v>
       </c>
@@ -3913,7 +3913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>29</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>29</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>29</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>29</v>
       </c>
@@ -4209,7 +4209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2020</v>
       </c>
@@ -4281,7 +4281,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="16" t="s">
         <v>29</v>
       </c>
@@ -4355,7 +4355,7 @@
         <v>3.02</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="16" t="s">
         <v>29</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="16" t="s">
         <v>29</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="16" t="s">
         <v>29</v>
       </c>
@@ -4577,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="16" t="s">
         <v>29</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
         <v>29</v>
       </c>
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="35">
         <v>2019</v>
       </c>
@@ -4797,7 +4797,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="11" t="s">
         <v>29</v>
       </c>
@@ -4871,7 +4871,7 @@
         <v>2.34</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="11" t="s">
         <v>29</v>
       </c>
@@ -4945,7 +4945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="11" t="s">
         <v>29</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>2018</v>
       </c>
@@ -5091,7 +5091,7 @@
         <v>5.26</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>2017</v>
       </c>
@@ -5163,7 +5163,7 @@
         <v>8.36</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>2016</v>
       </c>
@@ -5235,7 +5235,7 @@
         <v>5.28</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>2015</v>
       </c>
@@ -5307,7 +5307,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37" t="s">
         <v>51</v>
       </c>
